--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261021.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261021.xlsx
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>12,526,000</t>
+          <t>2,360,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,360,000</t>
+          <t>12,526,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>17,752,000</t>
+          <t>15,875,073</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>15,875,073</t>
+          <t>17,752,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2,943,000</t>
+          <t>14,568,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>14,568,000</t>
+          <t>2,943,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>8,119,597</t>
+          <t>3,881,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,881,000</t>
+          <t>8,119,597</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
